--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_957_Thailand_Gulf_of_Thailand.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_957_Thailand_Gulf_of_Thailand.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R96467ce0dc7d4784"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R2000c733a07247ba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Re2d731b0e8ab4c3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="Rb66081e2e3d64a3e"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R83ef4d842e604a3c"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R0a8f018ae16f487f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Re13386ca646e477f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="Rdd8a1506cdd64dff"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R0dd006ce7f584461"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R3a09f1ddf26c467d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R9e1a4f2395da474c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rbf55aa5b64d84aac"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ957CommercialTable" displayName="EEZ957CommercialTable" ref="A1:O11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O11"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ957CommercialTable" displayName="EEZ957CommercialTable" ref="A1:E11" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E11"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ957FunctionalTable" displayName="EEZ957FunctionalTable" ref="A1:O20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O20"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ957FunctionalTable" displayName="EEZ957FunctionalTable" ref="A1:E20" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E20"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ957ValidationTable" displayName="EEZ957ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ957ValidationTable" displayName="EEZ957ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -4647,7 +4601,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R743245bfd71f4775"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R35e9e78fe57f4367"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -4657,20 +4611,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -4678,606 +4622,212 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>146954.0672195994</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.2</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>158.48931924611142</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>146954.0672195994</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$60,A2,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>23290650.074081607</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.2</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>158.48931924611142</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>23290650.074081607</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>106994.0230725569</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>2.746670247511138</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>55.80463186610322</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>106994.0230725569</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>89.23849838168272</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$60,A3,'Species'!$U$2:$U$60))</x:f>
-        <x:v>9547985.954810092</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>2.746670247511138</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>55.80463186610322</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>5970762.069437392</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>3577223.8853727</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.5991235027909547</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.5991235027909547</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>416.2367967645</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>416.2367967645</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$60,A4,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>1021740.1760539954</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
-        <x:v>1021740.1760539954</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>103389.9989006993</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>2.84168649588663</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>69.45227814992072</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>103389.9989006993</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>135.3838239232239</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$60,A5,'Species'!$U$2:$U$60))</x:f>
-        <x:v>13997333.406594586</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>2.84168649588663</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>69.45227814992072</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>7180670.961571365</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>6816662.445023221</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.9493071721993391</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.949307172199339</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>36019.626730407</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>2.0216108400375044</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>10.510196604238617</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>36019.626730407</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>10.559559565592876</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$60,A6,'Species'!$U$2:$U$60))</x:f>
-        <x:v>380351.3939901541</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>2.0216108400375044</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>10.510196604238617</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>378573.35854786617</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1778.0354422879172</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0046966734508422</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.004696673450842171</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>12</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>235876.25217079857</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.832719873667397</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>680.3303940226441</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>235876.25217079857</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>989.4962210905114</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$60,A7,'Species'!$U$2:$U$60))</x:f>
-        <x:v>233398660.16799772</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.832719873667397</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>680.3303940226441</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>160473783.57994395</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>72924876.58805376</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.4544348301710257</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.4544348301710257</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>24</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>644440.128433602</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.6095280409644923</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>406.9378075951037</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>644440.128433602</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>608.4329714856995</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$60,A8,'Species'!$U$2:$U$60))</x:f>
-        <x:v>392098622.2874823</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.6095280409644923</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>406.9378075951037</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>262247052.99107707</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>129851569.29640526</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.495149775051327</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.49514977505132707</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>40329.318471720704</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.9000000000000004</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>794.3282347242822</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>40329.318471720704</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>794.3282347242813</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$60,A9,'Species'!$U$2:$U$60))</x:f>
-        <x:v>32034716.349275257</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.9000000000000004</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>794.3282347242822</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>32034716.349275295</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>-3.725290298461914e-8</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>0.9999999999999989</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>-1.1628916135373209e-15</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>2517.8727224348</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.78084292008026</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>603.7302267675145</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>2517.8727224348</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>634.9167353472576</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$60,A10,'Species'!$U$2:$U$60))</x:f>
-        <x:v>1598639.5289482148</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.78084292008026</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>603.7302267675145</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>1520115.8696873009</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>78523.65926091396</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0516563643777148</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.051656364377714745</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>10028.7869241279</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.5</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>3162.2776601683795</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>10028.7869241279</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$60,A11,'Species'!$U$2:$U$60))</x:f>
-        <x:v>31713808.848758414</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.5</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>3162.2776601683795</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>31713808.848758418</x:v>
       </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>-3.725290298461914e-9</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>0.9999999999999999</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>-1.1746587476224123e-16</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G11">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O11">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R05a39e65a0744851"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0643d1f31b304fdc"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -5287,20 +4837,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -5308,1092 +4848,383 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>98777.7110973716</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8392088946281477</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>690.5718874278163</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>98777.7110973716</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>718.0129027762893</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$60,A2,'Species'!$U$2:$U$60))</x:f>
-        <x:v>70923671.07462147</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8392088946281477</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>690.5718874278163</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>68213110.38831146</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>2710560.686310008</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0397366528352074</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.039736652835207345</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Jellyfish</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>3392.8256918604</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>3.46</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>288.40315031266056</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>3392.8256918604</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$60,A3,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>978501.6179942716</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>3.46</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>288.40315031266056</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>978501.6179942716</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>9834.0982007401</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.304050738881705</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2013.9595282035193</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>9834.0982007401</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2079.311466504065</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$60,A4,'Species'!$U$2:$U$60))</x:f>
-        <x:v>20448153.15152588</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.304050738881705</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2013.9595282035193</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>19805475.77266961</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>642677.3788562715</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0324494794385666</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0324494794385666</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>3076.1890395431</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>4.373915859882685</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>2365.461369124072</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>3076.1890395431</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>2366.361502129572</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$60,A5,'Species'!$U$2:$U$60))</x:f>
-        <x:v>7279375.316447736</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>4.373915859882685</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>2365.461369124072</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>7276606.337162086</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>2768.9792856499553</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0003805316870735</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.0003805316870734925</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>37447.9265079803</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.416864761116428</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2611.348056504821</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>37447.9265079803</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2635.2252615236903</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$60,A6,'Species'!$U$2:$U$60))</x:f>
-        <x:v>98683721.92551233</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.416864761116428</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2611.348056504821</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>97789570.10674973</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>894151.8187626004</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.0091436317573186</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.009143631757318497</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>2053.6462714548998</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.72</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>524.8074602497728</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>2053.6462714548998</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$60,A7,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>1077768.8839736616</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.72</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>524.8074602497728</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
-        <x:v>1077768.8839736616</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>464.2264509799</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>4.05</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>1122.018454301963</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>464.2264509799</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$60,A8,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>520870.6449745534</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>4.05</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>1122.018454301963</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
-        <x:v>520870.6449745534</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>41434.592468290495</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>2.4965136033689537</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>31.36993388395404</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>41434.592468290495</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>32.91366130474342</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$60,A9,'Species'!$U$2:$U$60))</x:f>
-        <x:v>1363764.142801386</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>2.4965136033689537</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>31.36993388395404</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1299800.4262388528</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>63963.716562533285</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0492104135922011</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.049210413592201144</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>7476.726157072801</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.955842435883567</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>90.33216848339337</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>7476.726157072801</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>93.10487362163526</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$60,A10,'Species'!$U$2:$U$60))</x:f>
-        <x:v>696119.6439578378</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.955842435883567</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>90.33216848339337</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>675388.8869248945</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>20730.757032943307</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.0306945486286165</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.030694548628616442</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>213360.0982276743</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.833027931596131</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>680.8131436992243</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>213360.0982276743</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>992.9496202231189</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$60,A11,'Species'!$U$2:$U$60))</x:f>
-        <x:v>211855828.50593653</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.833027931596131</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>680.8131436992243</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>145258359.2143582</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>66597469.29157832</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.4584759848023634</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.4584759848023633</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>228922.37974357037</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>3.788913840709162</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>615.0548404298831</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>228922.37974357037</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>828.5721017334367</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$60,A12,'Species'!$U$2:$U$60))</x:f>
-        <x:v>189678697.31795004</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>3.788913840709162</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>615.0548404298831</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>140799817.74401078</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>48878879.573939264</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.3471515827016647</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.34715158270166463</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>29989.367838603102</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.7886521700055296</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>614.6843697837035</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>29989.367838603102</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>761.4965157684774</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$60,A13,'Species'!$U$2:$U$60))</x:f>
-        <x:v>22836799.119195495</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.7886521700055296</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>614.6843697837035</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>18433995.670083415</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>4402803.44911208</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.2388415147703111</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.23884151477031118</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>37459.9047493989</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>2.0373128001525522</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>10.897146766235005</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>37459.9047493989</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>11.18841547912253</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$60,A14,'Species'!$U$2:$U$60))</x:f>
-        <x:v>419116.9781446302</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>2.0373128001525522</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>10.897146766235005</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>408206.0799033835</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>10910.898241246701</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.0267288969430077</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.02672889694300769</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>65559.43060426641</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>2.9047731856808308</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>80.31065827831677</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>65559.43060426641</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>124.83668232890507</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$60,A15,'Species'!$U$2:$U$60))</x:f>
-        <x:v>8184221.812008703</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>2.9047731856808308</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>80.31065827831677</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>5265121.028180262</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>2919100.783828441</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.5544223519658282</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.5544223519658283</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>149638.6218022583</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.24</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>173.78008287493762</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>149638.6218022583</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$60,A16,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>26004212.098087896</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.24</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>173.78008287493762</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
-        <x:v>26004212.098087896</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>140576.7668581577</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>3.511404665133438</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>324.64197003007405</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>140576.7668581577</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>324.7847583920632</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$60,A17,'Species'!$U$2:$U$60))</x:f>
-        <x:v>45657191.259564154</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>3.511404665133438</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>324.64197003007405</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>45637118.53329074</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>20072.726273417473</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0004398333400206</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.00043983334002069166</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>245161.082392387</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.027749918085653</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>106.5982114772381</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>245161.082392387</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>118.5894089304895</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$60,A18,'Species'!$U$2:$U$60))</x:f>
-        <x:v>29073507.85367221</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.027749918085653</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>106.5982114772381</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>26133732.906852264</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>2939774.946819946</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.1124896683263008</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.11248966832630088</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>11924.480544337</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.3</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>199.52623149688787</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>11924.480544337</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>199.5262314968879</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$60,A19,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>2379246.66556952</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.3</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>199.52623149688787</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>2379246.66556952</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>416.2367967645</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>4.39</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>2454.7089156850284</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>416.2367967645</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$60,A20,'Species'!$U$2:$U$60))</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>1021740.1760539954</x:v>
       </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>4.39</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>2454.7089156850284</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
-        <x:v>1021740.1760539954</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G20">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O20">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R22782cd1353b4d9e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf068893ff25e49bd"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6568,7 +5399,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -6667,7 +5498,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>739082508.1879923</x:v>
+        <x:v>525831874.2784343</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6681,7 +5512,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>739082508.1879923</x:v>
+        <x:v>608978643.1813896</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6695,7 +5526,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-213250633.90955806</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6709,7 +5540,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>0</x:v>
+        <x:v>-130103865.00660276</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -6720,9 +5551,9 @@
         <x:v>EEZ_957</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -6734,47 +5565,19 @@
         <x:v>EEZ_957</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_957</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_957</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf4be08a4473540a5"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R4efe87567343405b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -6821,7 +5624,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
